--- a/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Visits.xlsx
@@ -31,16 +31,16 @@
     <t>Snowbowl</t>
   </si>
   <si>
+    <t>Snowbowl Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45982</v>
+        <v>45981</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>45982</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="C4" s="2">
-        <v>44</v>
+        <v>1204</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45983</v>
+        <v>45985</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45983</v>
+        <v>45985</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45984</v>
+        <v>45986</v>
       </c>
       <c r="C8" s="2">
-        <v>288</v>
+        <v>999</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45985</v>
+        <v>45988</v>
       </c>
       <c r="C10" s="2">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45985</v>
+        <v>45990</v>
       </c>
       <c r="C11" s="2">
-        <v>1280</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45987</v>
+        <v>45990</v>
       </c>
       <c r="C12" s="2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +585,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45987</v>
+        <v>45991</v>
       </c>
       <c r="C13" s="2">
-        <v>243</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -599,13 +599,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45988</v>
+        <v>45992</v>
       </c>
       <c r="C14" s="2">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45988</v>
+        <v>45994</v>
       </c>
       <c r="C15" s="2">
-        <v>672</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45990</v>
+        <v>45995</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45990</v>
+        <v>45998</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45991</v>
+        <v>45998</v>
       </c>
       <c r="C18" s="2">
-        <v>964</v>
+        <v>166</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="C19" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="C20" s="2">
-        <v>593</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="C21" s="2">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="C23" s="2">
-        <v>1091</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="C24" s="2">
-        <v>1058</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="C25" s="2">
-        <v>85</v>
+        <v>1588</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +767,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="C26" s="2">
-        <v>4</v>
+        <v>339</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C27" s="2">
-        <v>1080</v>
+        <v>71</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="C28" s="2">
-        <v>133</v>
+        <v>661</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,10 +809,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>46005</v>
+        <v>46007</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>1416</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -823,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>46005</v>
+        <v>45965</v>
       </c>
       <c r="C30" s="2">
-        <v>1548</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>46006</v>
+        <v>45969</v>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>434</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>46006</v>
+        <v>45980</v>
       </c>
       <c r="C32" s="2">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="C33" s="2">
-        <v>27</v>
+        <v>1451</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,7 +882,7 @@
         <v>45982</v>
       </c>
       <c r="C34" s="2">
-        <v>15</v>
+        <v>570</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +896,10 @@
         <v>45983</v>
       </c>
       <c r="C35" s="2">
-        <v>1204</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45984</v>
+        <v>45983</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>45985</v>
       </c>
       <c r="C37" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,7 +938,7 @@
         <v>45985</v>
       </c>
       <c r="C38" s="2">
-        <v>2</v>
+        <v>1228</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>45986</v>
       </c>
       <c r="C39" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="C40" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45988</v>
+        <v>45986</v>
       </c>
       <c r="C41" s="2">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45990</v>
+        <v>45988</v>
       </c>
       <c r="C42" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45990</v>
+        <v>45989</v>
       </c>
       <c r="C43" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="C44" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="C45" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45994</v>
+        <v>45989</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45995</v>
+        <v>45990</v>
       </c>
       <c r="C47" s="2">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C49" s="2">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>46000</v>
+        <v>45991</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>46001</v>
+        <v>45992</v>
       </c>
       <c r="C51" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>46001</v>
+        <v>45992</v>
       </c>
       <c r="C52" s="2">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1145,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="C53" s="2">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>6</v>
@@ -1159,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>46003</v>
+        <v>45994</v>
       </c>
       <c r="C54" s="2">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>46004</v>
+        <v>45995</v>
       </c>
       <c r="C55" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>46004</v>
+        <v>45996</v>
       </c>
       <c r="C56" s="2">
-        <v>1588</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>46005</v>
+        <v>45997</v>
       </c>
       <c r="C57" s="2">
-        <v>339</v>
+        <v>64</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>6</v>
@@ -1215,13 +1215,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>46006</v>
+        <v>45998</v>
       </c>
       <c r="C58" s="2">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1229,13 +1229,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>46006</v>
+        <v>45999</v>
       </c>
       <c r="C59" s="2">
-        <v>661</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C60" s="2">
-        <v>1416</v>
+        <v>79</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1257,13 +1257,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45965</v>
+        <v>46001</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1271,10 +1271,10 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45969</v>
+        <v>46002</v>
       </c>
       <c r="C62" s="2">
-        <v>434</v>
+        <v>11</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>6</v>
@@ -1285,13 +1285,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>741</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1299,13 +1299,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45982</v>
+        <v>46003</v>
       </c>
       <c r="C64" s="2">
-        <v>1451</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1313,13 +1313,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45982</v>
+        <v>46004</v>
       </c>
       <c r="C65" s="2">
-        <v>570</v>
+        <v>417</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1327,13 +1327,13 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45983</v>
+        <v>46005</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1341,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45983</v>
+        <v>46005</v>
       </c>
       <c r="C67" s="2">
-        <v>136</v>
+        <v>993</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1355,13 +1355,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45985</v>
+        <v>46007</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1369,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45985</v>
+        <v>46007</v>
       </c>
       <c r="C69" s="2">
-        <v>1228</v>
+        <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1383,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45986</v>
+        <v>45968</v>
       </c>
       <c r="C70" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1397,13 +1397,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45986</v>
+        <v>45968</v>
       </c>
       <c r="C71" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="C72" s="2">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1425,13 +1425,13 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45988</v>
+        <v>45981</v>
       </c>
       <c r="C73" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1439,13 +1439,13 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45989</v>
+        <v>45983</v>
       </c>
       <c r="C74" s="2">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45989</v>
+        <v>45984</v>
       </c>
       <c r="C75" s="2">
         <v>5</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1467,13 +1467,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45989</v>
+        <v>45984</v>
       </c>
       <c r="C76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1481,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45989</v>
+        <v>45984</v>
       </c>
       <c r="C77" s="2">
-        <v>281</v>
+        <v>947</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1495,13 +1495,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45990</v>
+        <v>45986</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,13 +1509,13 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45991</v>
+        <v>45987</v>
       </c>
       <c r="C79" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1523,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45991</v>
+        <v>45987</v>
       </c>
       <c r="C80" s="2">
-        <v>2</v>
+        <v>1431</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1537,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="C81" s="2">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1551,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C83" s="2">
-        <v>1</v>
+        <v>1625</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45994</v>
+        <v>45990</v>
       </c>
       <c r="C84" s="2">
-        <v>2</v>
+        <v>368</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1593,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="C85" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,13 +1621,13 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1635,10 +1635,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45997</v>
+        <v>45993</v>
       </c>
       <c r="C88" s="2">
-        <v>64</v>
+        <v>738</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1649,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C89" s="2">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1663,13 +1663,13 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C90" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1677,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>46000</v>
+        <v>45996</v>
       </c>
       <c r="C91" s="2">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1691,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>46001</v>
+        <v>45996</v>
       </c>
       <c r="C92" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,13 +1705,13 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>46002</v>
+        <v>45997</v>
       </c>
       <c r="C93" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1719,13 +1719,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>46002</v>
+        <v>45997</v>
       </c>
       <c r="C94" s="2">
-        <v>741</v>
+        <v>1192</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1733,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>46003</v>
+        <v>45999</v>
       </c>
       <c r="C95" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1747,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>46004</v>
+        <v>45999</v>
       </c>
       <c r="C96" s="2">
-        <v>417</v>
+        <v>97</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C97" s="2">
-        <v>12</v>
+        <v>570</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,13 +1775,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>46005</v>
+        <v>46001</v>
       </c>
       <c r="C98" s="2">
-        <v>993</v>
+        <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1789,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C99" s="2">
-        <v>77</v>
+        <v>997</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>6</v>
@@ -1803,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="C100" s="2">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1817,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45968</v>
+        <v>46007</v>
       </c>
       <c r="C101" s="2">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45968</v>
+        <v>45981</v>
       </c>
       <c r="C102" s="2">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,13 +1845,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="C103" s="2">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1859,13 +1859,13 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45981</v>
+        <v>45983</v>
       </c>
       <c r="C104" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1873,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="C105" s="2">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1887,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="C106" s="2">
-        <v>5</v>
+        <v>178</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,13 +1901,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45984</v>
+        <v>45986</v>
       </c>
       <c r="C107" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1915,13 +1915,13 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45984</v>
+        <v>45988</v>
       </c>
       <c r="C108" s="2">
-        <v>948</v>
+        <v>558</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1929,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="C109" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="C110" s="2">
-        <v>3</v>
+        <v>1141</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,13 +1957,13 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45987</v>
+        <v>45990</v>
       </c>
       <c r="C111" s="2">
-        <v>1431</v>
+        <v>4</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1971,13 +1971,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C112" s="2">
-        <v>39</v>
+        <v>363</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1985,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C113" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1999,13 +1999,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C114" s="2">
-        <v>1625</v>
+        <v>656</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2013,13 +2013,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C115" s="2">
-        <v>368</v>
+        <v>797</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2027,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45991</v>
+        <v>45995</v>
       </c>
       <c r="C116" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,13 +2041,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="C117" s="2">
-        <v>61</v>
+        <v>803</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2055,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="C118" s="2">
-        <v>3</v>
+        <v>865</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2069,10 +2069,10 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="C119" s="2">
-        <v>738</v>
+        <v>93</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -2083,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45993</v>
+        <v>45997</v>
       </c>
       <c r="C120" s="2">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>6</v>
@@ -2097,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="C121" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,10 +2111,10 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>1401</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2125,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="C123" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,13 +2139,13 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="C124" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2153,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="C125" s="2">
-        <v>1192</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C126" s="2">
-        <v>7</v>
+        <v>1004</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2181,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="C127" s="2">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>6</v>
@@ -2195,13 +2195,13 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C128" s="2">
-        <v>570</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2209,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C129" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,10 +2226,10 @@
         <v>46003</v>
       </c>
       <c r="C130" s="2">
-        <v>997</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2240,10 +2240,10 @@
         <v>46004</v>
       </c>
       <c r="C131" s="2">
-        <v>245</v>
+        <v>5</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,13 +2251,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>46007</v>
+        <v>46005</v>
       </c>
       <c r="C132" s="2">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2265,13 +2265,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45969</v>
+        <v>46005</v>
       </c>
       <c r="C133" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,13 +2279,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45969</v>
+        <v>46005</v>
       </c>
       <c r="C134" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2293,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45975</v>
+        <v>46005</v>
       </c>
       <c r="C135" s="2">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2307,13 +2307,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45983</v>
+        <v>46007</v>
       </c>
       <c r="C136" s="2">
-        <v>947</v>
+        <v>6</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2321,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45984</v>
+        <v>46007</v>
       </c>
       <c r="C137" s="2">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2335,10 +2335,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45986</v>
+        <v>45971</v>
       </c>
       <c r="C138" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,13 +2349,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45986</v>
+        <v>45975</v>
       </c>
       <c r="C139" s="2">
-        <v>1213</v>
+        <v>1</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2363,13 +2363,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45987</v>
+        <v>45981</v>
       </c>
       <c r="C140" s="2">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2377,13 +2377,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45989</v>
+        <v>45983</v>
       </c>
       <c r="C141" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45989</v>
+        <v>45983</v>
       </c>
       <c r="C142" s="2">
-        <v>1402</v>
+        <v>243</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,13 +2405,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45990</v>
+        <v>45984</v>
       </c>
       <c r="C143" s="2">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2419,13 +2419,13 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45990</v>
+        <v>45984</v>
       </c>
       <c r="C144" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2433,13 +2433,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45990</v>
+        <v>45984</v>
       </c>
       <c r="C145" s="2">
-        <v>239</v>
+        <v>1514</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2447,13 +2447,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45992</v>
+        <v>45986</v>
       </c>
       <c r="C146" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2461,13 +2461,13 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>45993</v>
+        <v>45987</v>
       </c>
       <c r="C147" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2475,13 +2475,13 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45993</v>
+        <v>45987</v>
       </c>
       <c r="C148" s="2">
-        <v>67</v>
+        <v>1034</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2489,13 +2489,13 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45994</v>
+        <v>45988</v>
       </c>
       <c r="C149" s="2">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2503,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45995</v>
+        <v>45990</v>
       </c>
       <c r="C150" s="2">
-        <v>67</v>
+        <v>962</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2517,13 +2517,13 @@
         <v>4</v>
       </c>
       <c r="B151" s="2">
-        <v>45997</v>
+        <v>45991</v>
       </c>
       <c r="C151" s="2">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,13 +2531,13 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2545,13 +2545,13 @@
         <v>4</v>
       </c>
       <c r="B153" s="2">
-        <v>45998</v>
+        <v>45994</v>
       </c>
       <c r="C153" s="2">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2559,13 +2559,13 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45998</v>
+        <v>45994</v>
       </c>
       <c r="C154" s="2">
-        <v>1151</v>
+        <v>53</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,13 +2573,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45999</v>
+        <v>45997</v>
       </c>
       <c r="C155" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2587,13 +2587,13 @@
         <v>4</v>
       </c>
       <c r="B156" s="2">
-        <v>46000</v>
+        <v>45997</v>
       </c>
       <c r="C156" s="2">
+        <v>173</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2601,10 +2601,10 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C157" s="2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>6</v>
@@ -2615,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C158" s="2">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,10 +2629,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C159" s="2">
-        <v>725</v>
+        <v>913</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2643,13 +2643,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C160" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>46003</v>
       </c>
       <c r="C161" s="2">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>6</v>
@@ -2671,10 +2671,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>46004</v>
+        <v>46003</v>
       </c>
       <c r="C162" s="2">
-        <v>70</v>
+        <v>1104</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,10 +2688,10 @@
         <v>46004</v>
       </c>
       <c r="C163" s="2">
-        <v>847</v>
+        <v>2</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2699,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>46005</v>
+        <v>46004</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2713,13 +2713,13 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>46006</v>
+        <v>46005</v>
       </c>
       <c r="C165" s="2">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2727,13 +2727,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C166" s="2">
-        <v>574</v>
+        <v>5</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2741,10 +2741,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45969</v>
+        <v>46006</v>
       </c>
       <c r="C167" s="2">
-        <v>4</v>
+        <v>1389</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2755,13 +2755,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45982</v>
+        <v>46006</v>
       </c>
       <c r="C168" s="2">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2769,13 +2769,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45982</v>
+        <v>46007</v>
       </c>
       <c r="C169" s="2">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2783,13 +2783,13 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C170" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2797,13 +2797,13 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C171" s="2">
         <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2811,13 +2811,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C172" s="2">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2825,10 +2825,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45986</v>
+        <v>45983</v>
       </c>
       <c r="C173" s="2">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>6</v>
@@ -2839,13 +2839,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45987</v>
+        <v>45983</v>
       </c>
       <c r="C174" s="2">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2853,13 +2853,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45988</v>
+        <v>45983</v>
       </c>
       <c r="C175" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2867,13 +2867,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45988</v>
+        <v>45984</v>
       </c>
       <c r="C176" s="2">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2881,13 +2881,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C177" s="2">
-        <v>1277</v>
+        <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2895,10 +2895,10 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="C178" s="2">
-        <v>462</v>
+        <v>52</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>6</v>
@@ -2909,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45990</v>
+        <v>45985</v>
       </c>
       <c r="C179" s="2">
-        <v>3</v>
+        <v>1280</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2923,13 +2923,13 @@
         <v>4</v>
       </c>
       <c r="B180" s="2">
-        <v>45990</v>
+        <v>45987</v>
       </c>
       <c r="C180" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2937,13 +2937,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45991</v>
+        <v>45987</v>
       </c>
       <c r="C181" s="2">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2951,13 +2951,13 @@
         <v>4</v>
       </c>
       <c r="B182" s="2">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="C182" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2965,13 +2965,13 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="C183" s="2">
-        <v>1317</v>
+        <v>672</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2979,10 +2979,10 @@
         <v>4</v>
       </c>
       <c r="B184" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C184" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>6</v>
@@ -2993,13 +2993,13 @@
         <v>4</v>
       </c>
       <c r="B185" s="2">
-        <v>45993</v>
+        <v>45990</v>
       </c>
       <c r="C185" s="2">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3007,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45993</v>
+        <v>45991</v>
       </c>
       <c r="C186" s="2">
-        <v>488</v>
+        <v>964</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3021,13 +3021,13 @@
         <v>4</v>
       </c>
       <c r="B187" s="2">
-        <v>45994</v>
+        <v>45993</v>
       </c>
       <c r="C187" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3038,10 +3038,10 @@
         <v>45994</v>
       </c>
       <c r="C188" s="2">
-        <v>712</v>
+        <v>593</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3049,13 +3049,13 @@
         <v>4</v>
       </c>
       <c r="B189" s="2">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="C189" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3063,10 +3063,10 @@
         <v>4</v>
       </c>
       <c r="B190" s="2">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="C190" s="2">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>6</v>
@@ -3080,7 +3080,7 @@
         <v>45996</v>
       </c>
       <c r="C191" s="2">
-        <v>94</v>
+        <v>1091</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3091,10 +3091,10 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="C192" s="2">
-        <v>1326</v>
+        <v>1058</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3105,13 +3105,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45997</v>
+        <v>46000</v>
       </c>
       <c r="C193" s="2">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3119,13 +3119,13 @@
         <v>4</v>
       </c>
       <c r="B194" s="2">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="C194" s="2">
-        <v>1627</v>
+        <v>4</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45998</v>
+        <v>46002</v>
       </c>
       <c r="C195" s="2">
-        <v>21</v>
+        <v>1080</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3147,13 +3147,13 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45998</v>
+        <v>46003</v>
       </c>
       <c r="C196" s="2">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3161,13 +3161,13 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C197" s="2">
-        <v>718</v>
+        <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3175,10 +3175,10 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C198" s="2">
-        <v>1</v>
+        <v>1548</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>5</v>
@@ -3189,13 +3189,13 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C199" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3203,13 +3203,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C200" s="2">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,13 +3217,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>46003</v>
+        <v>45969</v>
       </c>
       <c r="C201" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3231,13 +3231,13 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45971</v>
+        <v>45969</v>
       </c>
       <c r="C202" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,10 +3248,10 @@
         <v>45975</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3259,10 +3259,10 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45981</v>
+        <v>45983</v>
       </c>
       <c r="C204" s="2">
-        <v>265</v>
+        <v>947</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3273,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3287,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="B206" s="2">
-        <v>45983</v>
+        <v>45986</v>
       </c>
       <c r="C206" s="2">
-        <v>243</v>
+        <v>5</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>6</v>
@@ -3301,10 +3301,10 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45984</v>
+        <v>45986</v>
       </c>
       <c r="C207" s="2">
-        <v>37</v>
+        <v>1213</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>5</v>
@@ -3315,13 +3315,13 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45984</v>
+        <v>45987</v>
       </c>
       <c r="C208" s="2">
-        <v>3</v>
+        <v>285</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3329,13 +3329,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45984</v>
+        <v>45989</v>
       </c>
       <c r="C209" s="2">
-        <v>1514</v>
+        <v>12</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3343,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="C210" s="2">
-        <v>2</v>
+        <v>1400</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3357,13 +3357,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45987</v>
+        <v>45990</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3371,13 +3371,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45987</v>
+        <v>45990</v>
       </c>
       <c r="C212" s="2">
-        <v>1034</v>
+        <v>6</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3385,13 +3385,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45988</v>
+        <v>45990</v>
       </c>
       <c r="C213" s="2">
         <v>239</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C214" s="2">
-        <v>962</v>
+        <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3413,13 +3413,13 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45991</v>
+        <v>45993</v>
       </c>
       <c r="C215" s="2">
-        <v>197</v>
+        <v>8</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3427,13 +3427,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="C216" s="2">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3444,10 +3444,10 @@
         <v>45994</v>
       </c>
       <c r="C217" s="2">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3455,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="C218" s="2">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,10 +3472,10 @@
         <v>45997</v>
       </c>
       <c r="C219" s="2">
-        <v>3</v>
+        <v>235</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>45997</v>
       </c>
       <c r="C220" s="2">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3497,13 +3497,13 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45999</v>
+        <v>45998</v>
       </c>
       <c r="C221" s="2">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3511,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>46000</v>
+        <v>45998</v>
       </c>
       <c r="C222" s="2">
-        <v>5</v>
+        <v>1151</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3525,13 +3525,13 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C223" s="2">
-        <v>913</v>
+        <v>2</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3539,13 +3539,13 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C224" s="2">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3553,13 +3553,13 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="C225" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3567,13 +3567,13 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C226" s="2">
-        <v>1104</v>
+        <v>97</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3581,13 +3581,13 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>46004</v>
+        <v>46001</v>
       </c>
       <c r="C227" s="2">
-        <v>2</v>
+        <v>725</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3595,13 +3595,13 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>46004</v>
+        <v>46003</v>
       </c>
       <c r="C228" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3609,13 +3609,13 @@
         <v>4</v>
       </c>
       <c r="B229" s="2">
-        <v>46005</v>
+        <v>46003</v>
       </c>
       <c r="C229" s="2">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3623,13 +3623,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="C230" s="2">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3637,13 +3637,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="C231" s="2">
-        <v>1389</v>
+        <v>847</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,10 +3651,10 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>46006</v>
+        <v>46005</v>
       </c>
       <c r="C232" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>6</v>
@@ -3665,13 +3665,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C233" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3679,13 +3679,13 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45981</v>
+        <v>46007</v>
       </c>
       <c r="C234" s="2">
-        <v>34</v>
+        <v>574</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3693,10 +3693,10 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45982</v>
+        <v>45969</v>
       </c>
       <c r="C235" s="2">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>6</v>
@@ -3707,13 +3707,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="C236" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3721,13 +3721,13 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45984</v>
+        <v>45982</v>
       </c>
       <c r="C237" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>45985</v>
       </c>
       <c r="C238" s="2">
-        <v>178</v>
+        <v>3</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>6</v>
@@ -3749,13 +3749,13 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="C239" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3763,13 +3763,13 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C240" s="2">
-        <v>558</v>
+        <v>134</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3777,13 +3777,13 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="C241" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3791,13 +3791,13 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="C242" s="2">
-        <v>1141</v>
+        <v>42</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3805,13 +3805,13 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45990</v>
+        <v>45988</v>
       </c>
       <c r="C243" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3819,10 +3819,10 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="C244" s="2">
-        <v>363</v>
+        <v>2</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>6</v>
@@ -3833,10 +3833,10 @@
         <v>4</v>
       </c>
       <c r="B245" s="2">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="C245" s="2">
-        <v>11</v>
+        <v>1277</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>5</v>
@@ -3847,13 +3847,13 @@
         <v>4</v>
       </c>
       <c r="B246" s="2">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="C246" s="2">
-        <v>656</v>
+        <v>462</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3861,13 +3861,13 @@
         <v>4</v>
       </c>
       <c r="B247" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C247" s="2">
-        <v>797</v>
+        <v>3</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3875,13 +3875,13 @@
         <v>4</v>
       </c>
       <c r="B248" s="2">
-        <v>45995</v>
+        <v>45990</v>
       </c>
       <c r="C248" s="2">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3889,13 +3889,13 @@
         <v>4</v>
       </c>
       <c r="B249" s="2">
-        <v>45995</v>
+        <v>45991</v>
       </c>
       <c r="C249" s="2">
-        <v>803</v>
+        <v>17</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3903,13 +3903,13 @@
         <v>4</v>
       </c>
       <c r="B250" s="2">
-        <v>45995</v>
+        <v>45991</v>
       </c>
       <c r="C250" s="2">
-        <v>865</v>
+        <v>4</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3917,13 +3917,13 @@
         <v>4</v>
       </c>
       <c r="B251" s="2">
-        <v>45996</v>
+        <v>45991</v>
       </c>
       <c r="C251" s="2">
-        <v>93</v>
+        <v>1317</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3931,13 +3931,13 @@
         <v>4</v>
       </c>
       <c r="B252" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C252" s="2">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3945,13 +3945,13 @@
         <v>4</v>
       </c>
       <c r="B253" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C253" s="2">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3959,13 +3959,13 @@
         <v>4</v>
       </c>
       <c r="B254" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C254" s="2">
-        <v>1401</v>
+        <v>488</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3973,13 +3973,13 @@
         <v>4</v>
       </c>
       <c r="B255" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C255" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3987,10 +3987,10 @@
         <v>4</v>
       </c>
       <c r="B256" s="2">
-        <v>46001</v>
+        <v>45994</v>
       </c>
       <c r="C256" s="2">
-        <v>8</v>
+        <v>711</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>5</v>
@@ -4001,13 +4001,13 @@
         <v>4</v>
       </c>
       <c r="B257" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="C257" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4015,13 +4015,13 @@
         <v>4</v>
       </c>
       <c r="B258" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="C258" s="2">
-        <v>1004</v>
+        <v>64</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4029,13 +4029,13 @@
         <v>4</v>
       </c>
       <c r="B259" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C259" s="2">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4043,13 +4043,13 @@
         <v>4</v>
       </c>
       <c r="B260" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C260" s="2">
-        <v>1</v>
+        <v>1326</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4057,13 +4057,13 @@
         <v>4</v>
       </c>
       <c r="B261" s="2">
-        <v>46002</v>
+        <v>45997</v>
       </c>
       <c r="C261" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4071,10 +4071,10 @@
         <v>4</v>
       </c>
       <c r="B262" s="2">
-        <v>46003</v>
+        <v>45997</v>
       </c>
       <c r="C262" s="2">
-        <v>1</v>
+        <v>1627</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>5</v>
@@ -4085,13 +4085,13 @@
         <v>4</v>
       </c>
       <c r="B263" s="2">
-        <v>46004</v>
+        <v>45998</v>
       </c>
       <c r="C263" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4099,13 +4099,13 @@
         <v>4</v>
       </c>
       <c r="B264" s="2">
-        <v>46005</v>
+        <v>45998</v>
       </c>
       <c r="C264" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4113,13 +4113,13 @@
         <v>4</v>
       </c>
       <c r="B265" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C265" s="2">
-        <v>2</v>
+        <v>718</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4127,13 +4127,13 @@
         <v>4</v>
       </c>
       <c r="B266" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C266" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4141,13 +4141,13 @@
         <v>4</v>
       </c>
       <c r="B267" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C267" s="2">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4155,13 +4155,13 @@
         <v>4</v>
       </c>
       <c r="B268" s="2">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C268" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4169,13 +4169,13 @@
         <v>4</v>
       </c>
       <c r="B269" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C269" s="2">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
